--- a/inferences/jesuitas-entrada-desc.xlsx
+++ b/inferences/jesuitas-entrada-desc.xlsx
@@ -760,11 +760,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16091026 ou 1607"}}</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1160,11 +1156,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 17070718"}}</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1197,11 +1189,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "antes de, nesta data agradece o geral por lhe ter permitido entrar na companhia"}}</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -1498,11 +1486,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "o cat\u00e1logo do Jap\u00e3o de 1697 diz 1675"}}</t>
-        </is>
-      </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -1733,11 +1717,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "Goa?"}}</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -1869,11 +1849,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "pela segunda vez"}}</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -2269,11 +2245,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "volta a ser recebido na Companhia"}}</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -2471,11 +2443,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "entra como frade coadjutor"}, "value": {"comment": "suponho que na \u00cdndia"}}</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -2508,11 +2476,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "suponho que na \u00cdndia"}}</t>
-        </is>
-      </c>
+      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -2710,11 +2674,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "Pequim?"}}</t>
-        </is>
-      </c>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -2780,11 +2740,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "G\u00e9nova?"}}</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -2982,11 +2938,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "venu au service des P\u00e8res? recebido quatro meses antes da sua morte"}}</t>
-        </is>
-      </c>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -3415,11 +3367,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "era um letrado chin\u00eas que se tornou catequista e depois jesu\u00edta"}}</t>
-        </is>
-      </c>
+      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
@@ -3749,11 +3697,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 1567"}}</t>
-        </is>
-      </c>
+      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
@@ -4149,11 +4093,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "se for mesmo ele"}}</t>
-        </is>
-      </c>
+      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -4780,11 +4720,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 17401120"}}</t>
-        </is>
-      </c>
+      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
@@ -4817,11 +4753,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "Macau?"}}</t>
-        </is>
-      </c>
+      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
@@ -4887,11 +4819,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "La date de son E. est aussi variable, 16 ou 26 sept. 1682., JS 134, 417 dit 16 sept. 1683."}}</t>
-        </is>
-      </c>
+      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
@@ -5023,11 +4951,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16800902"}}</t>
-        </is>
-      </c>
+      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
@@ -5192,11 +5116,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "era j\u00e1 padre"}}</t>
-        </is>
-      </c>
+      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
@@ -5394,11 +5314,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16991031"}}</t>
-        </is>
-      </c>
+      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
@@ -5431,11 +5347,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "inscreve-se a 8 de Julho"}}</t>
-        </is>
-      </c>
+      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
@@ -5864,11 +5776,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"original": "gallo-belge"}}</t>
-        </is>
-      </c>
+      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
@@ -5934,11 +5842,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "Fran\u00e7a? @wikidata:Q142"}}</t>
-        </is>
-      </c>
+      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
@@ -6037,11 +5941,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "vice prov\u00edncia de Portugal"}}</t>
-        </is>
-      </c>
+      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
@@ -6074,11 +5974,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "admitido na Companhia depois de torturado pela f\u00e9?"}}</t>
-        </is>
-      </c>
+      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
@@ -6672,11 +6568,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16960918"}}</t>
-        </is>
-      </c>
+      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
@@ -6973,11 +6865,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "Lyon? @wikidata:Q456"}}</t>
-        </is>
-      </c>
+      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
@@ -7142,11 +7030,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 17321231"}}</t>
-        </is>
-      </c>
+      <c r="G200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
@@ -7344,11 +7228,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16800422"}}</t>
-        </is>
-      </c>
+      <c r="G206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
@@ -7678,11 +7558,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "alternativa"}}</t>
-        </is>
-      </c>
+      <c r="G216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
@@ -8078,11 +7954,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 1729"}}</t>
-        </is>
-      </c>
+      <c r="G228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
@@ -8148,11 +8020,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 1689"}}</t>
-        </is>
-      </c>
+      <c r="G230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
@@ -8350,11 +8218,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 19 ou 28"}}</t>
-        </is>
-      </c>
+      <c r="G236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
@@ -8721,11 +8585,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "cerca de"}}</t>
-        </is>
-      </c>
+      <c r="G247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
@@ -8923,11 +8783,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "segundo Pf."}}</t>
-        </is>
-      </c>
+      <c r="G253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
@@ -8960,11 +8816,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 1663"}}</t>
-        </is>
-      </c>
+      <c r="G254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
@@ -9063,11 +8915,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "a 15, 23 ou 25"}}</t>
-        </is>
-      </c>
+      <c r="G257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
@@ -9133,11 +8981,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "novi\u00e7o"}}</t>
-        </is>
-      </c>
+      <c r="G259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
@@ -9434,11 +9278,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "diz que esteve em miss\u00e3o num semestre em 1681, n\u00e3o est\u00e1 no cat\u00e1logo de 1683"}}</t>
-        </is>
-      </c>
+      <c r="G268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
@@ -9636,11 +9476,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16661211"}}</t>
-        </is>
-      </c>
+      <c r="G274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
@@ -9772,11 +9608,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 17221128"}}</t>
-        </is>
-      </c>
+      <c r="G278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
@@ -10110,11 +9942,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16460000"}}</t>
-        </is>
-      </c>
+      <c r="G288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
@@ -10477,11 +10305,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "se for ele"}}</t>
-        </is>
-      </c>
+      <c r="G299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
@@ -10547,11 +10371,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "estava j\u00e1 no noviciado"}}</t>
-        </is>
-      </c>
+      <c r="G301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
@@ -10751,7 +10571,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>talvez tenha saído durante o noviciado extra_info: {"value": {"comment": "para a China"}}</t>
+          <t>talvez tenha saído durante o noviciado</t>
         </is>
       </c>
     </row>
@@ -11050,11 +10870,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 17290802"}}</t>
-        </is>
-      </c>
+      <c r="G316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
@@ -11351,11 +11167,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "aparece inscrito, mas depois o seu nome \u00e9 repetio em \u00c9vora, 16970925, ter\u00e1 sa\u00eddo no entretanto?"}}</t>
-        </is>
-      </c>
+      <c r="G325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
@@ -11388,11 +11200,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "o cat\u00e1logo de 1717 diz 17170509, a primeira data vem do cat\u00e1logo de 1734"}}</t>
-        </is>
-      </c>
+      <c r="G326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
@@ -11524,11 +11332,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "para a China"}}</t>
-        </is>
-      </c>
+      <c r="G330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
@@ -11594,11 +11398,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 1634"}}</t>
-        </is>
-      </c>
+      <c r="G332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
@@ -11666,7 +11466,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>depois de libertado da escravatura extra_info: {"date": {"comment": "[depois de 1615 que \u00e9 a data da persegui\u00e7\u00e3o ao padre Sebasti\u00e3o Fernandes- JRC]"}}</t>
+          <t>depois de libertado da escravatura</t>
         </is>
       </c>
     </row>
@@ -12229,11 +12029,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "catequista"}}</t>
-        </is>
-      </c>
+      <c r="G351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="1" t="inlineStr">
@@ -12266,11 +12062,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16730930"}}</t>
-        </is>
-      </c>
+      <c r="G352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="1" t="inlineStr">
@@ -12369,11 +12161,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "no mar, pela data de embarque seria em Lisboa?", "original": "in mari"}}</t>
-        </is>
-      </c>
+      <c r="G355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="1" t="inlineStr">
@@ -12406,11 +12194,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 1581 segundo Wicki"}}</t>
-        </is>
-      </c>
+      <c r="G356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="1" t="inlineStr">
@@ -12542,11 +12326,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 16320000"}}</t>
-        </is>
-      </c>
+      <c r="G360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="1" t="inlineStr">
@@ -12975,11 +12755,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G373" t="inlineStr">
-        <is>
-          <t>extra_info: {"value": {"comment": "Toulouse? @wikidata:Q7880"}}</t>
-        </is>
-      </c>
+      <c r="G373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="1" t="inlineStr">
@@ -13144,11 +12920,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G378" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "em 1758 n\u00e3o era ainda Padre"}}</t>
-        </is>
-      </c>
+      <c r="G378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="1" t="inlineStr">
@@ -13379,11 +13151,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G385" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 15721228"}}</t>
-        </is>
-      </c>
+      <c r="G385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="1" t="inlineStr">
@@ -13449,11 +13217,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G387" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "cerca de"}}</t>
-        </is>
-      </c>
+      <c r="G387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="1" t="inlineStr">
@@ -13684,11 +13448,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G394" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 17490202"}}</t>
-        </is>
-      </c>
+      <c r="G394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="1" t="inlineStr">
@@ -13787,11 +13547,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G397" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 30 ou 29"}}</t>
-        </is>
-      </c>
+      <c r="G397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="1" t="inlineStr">
@@ -13824,11 +13580,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G398" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 1 de novembro"}}</t>
-        </is>
-      </c>
+      <c r="G398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="1" t="inlineStr">
@@ -13861,11 +13613,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G399" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 17480000"}}</t>
-        </is>
-      </c>
+      <c r="G399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="1" t="inlineStr">
@@ -14129,11 +13877,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="G407" t="inlineStr">
-        <is>
-          <t>extra_info: {"date": {"comment": "ou 17361104"}}</t>
-        </is>
-      </c>
+      <c r="G407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="1" t="inlineStr">

--- a/inferences/jesuitas-entrada-desc.xlsx
+++ b/inferences/jesuitas-entrada-desc.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G423"/>
+  <dimension ref="A1:G421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,12 +625,12 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>deh-fernao-martins</t>
+          <t>deh-antonio-pais</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fernão Martins</t>
+          <t>António Pais</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Évora</t>
+          <t>Toreguia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -654,12 +654,12 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-pais</t>
+          <t>deh-diogo-pinto</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>António Pais</t>
+          <t>Diogo Pinto</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Toreguia</t>
+          <t>Quintela, diocese de Miranda</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -677,18 +677,22 @@
           <t>15660000</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>15760307</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>deh-diogo-pinto</t>
+          <t>deh-fernao-martins</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Diogo Pinto</t>
+          <t>Fernão Martins</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -698,7 +702,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Quintela, diocese de Miranda</t>
+          <t>Évora</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -706,11 +710,7 @@
           <t>15660000</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>15760307</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1154,12 +1154,12 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>deh-pedro-de-francisco</t>
+          <t>deh-bento-de-gois</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pedro de Francisco</t>
+          <t>Bento de Góis</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Covilhã, diocese da Guarda</t>
+          <t>Vila Franca do Campo, ilha de S. Miguel, Açores</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1177,11 +1177,7 @@
           <t>1588</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>15890404</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1212,7 +1208,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>16110320</t>
+          <t>15890404</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1220,12 +1216,12 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>deh-bento-de-gois</t>
+          <t>deh-pedro-de-francisco</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bento de Góis</t>
+          <t>Pedro de Francisco</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1235,7 +1231,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Vila Franca do Campo, ilha de S. Miguel, Açores</t>
+          <t>Covilhã, diocese da Guarda</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1243,7 +1239,11 @@
           <t>1588</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>16110320</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -2290,12 +2290,12 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-ferreira</t>
+          <t>deh-joao-da-veiga</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>João Ferreira</t>
+          <t>João da Veiga</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Funchal, ilha da Madeira</t>
+          <t>Verros</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2323,12 +2323,12 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-da-veiga</t>
+          <t>deh-joao-ferreira</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>João da Veiga</t>
+          <t>João Ferreira</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Verros</t>
+          <t>Funchal, ilha da Madeira</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2674,12 +2674,12 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>deh-goncalo-martins</t>
+          <t>deh-antonio-de-torres</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Gonçalo Martins</t>
+          <t>António de Torres</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Poiares (Santiago)</t>
+          <t>Torres Vedras</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2703,12 +2703,12 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-de-torres</t>
+          <t>deh-goncalo-martins</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>António de Torres</t>
+          <t>Gonçalo Martins</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Torres Vedras</t>
+          <t>Poiares (Santiago)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2794,12 +2794,12 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>deh-inacio-lobo</t>
+          <t>deh-antonio-rodrigues-ii</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Inácio Lobo</t>
+          <t>António Rodrigues</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Covilhã, diocese da Guarda</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2827,12 +2827,12 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-rodrigues-ii</t>
+          <t>deh-inacio-lobo</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>António Rodrigues</t>
+          <t>Inácio Lobo</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Covilhã, diocese da Guarda</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2893,22 +2893,22 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>deh-baltasar-caldeira</t>
+          <t>deh-luis-da-gama</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Baltasar Caldeira</t>
+          <t>Luís da Gama</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>Lavre, diocese de Évora</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2916,18 +2916,22 @@
           <t>1625</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>16300418</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>deh-duarte-ferreira</t>
+          <t>deh-baltasar-caldeira</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Duarte Ferreira</t>
+          <t>Baltasar Caldeira</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2951,22 +2955,22 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>deh-luis-da-gama</t>
+          <t>deh-duarte-ferreira</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Luís da Gama</t>
+          <t>Duarte Ferreira</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Lavre, diocese de Évora</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2974,11 +2978,7 @@
           <t>1625</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>16300418</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
@@ -3418,22 +3418,22 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-nunes</t>
+          <t>deh-henri-xavier</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>João Nunes</t>
+          <t>Henri Xavier</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Montemor</t>
+          <t>?</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3441,32 +3441,28 @@
           <t>16320000</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>16400326</t>
-        </is>
-      </c>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>deh-henri-xavier</t>
+          <t>deh-joao-nunes</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Henri Xavier</t>
+          <t>João Nunes</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Montemor</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3474,7 +3470,11 @@
           <t>16320000</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>16400326</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Burgos</t>
+          <t>towns</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7446,12 +7446,12 @@
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>deh-inacio-lopes</t>
+          <t>deh-francisco-da-silva-i</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Inácio Lopes</t>
+          <t>Francisco da Silva</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Lamego</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -7469,22 +7469,18 @@
           <t>1681</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>1694</t>
-        </is>
-      </c>
+      <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-da-silva-i</t>
+          <t>deh-inacio-lopes</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Francisco da Silva</t>
+          <t>Inácio Lopes</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7494,7 +7490,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Lamego</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -7502,7 +7498,11 @@
           <t>1681</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>1694</t>
+        </is>
+      </c>
       <c r="G225" t="inlineStr"/>
     </row>
     <row r="226">
@@ -7793,12 +7793,12 @@
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>deh-jean-charles-etienne-froissard-de-broissia</t>
+          <t>deh-pierre-dalbissi</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Jean-Charles Etienne Froissard de Broissia</t>
+          <t>Pierre Dalbissi</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Dole, Jura</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -7816,22 +7816,18 @@
           <t>16820424</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>16980000</t>
-        </is>
-      </c>
+      <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>deh-pierre-dalbissi</t>
+          <t>deh-jean-charles-etienne-froissard-de-broissia</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Pierre Dalbissi</t>
+          <t>Jean-Charles Etienne Froissard de Broissia</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7841,7 +7837,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Dole, Jura</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -7849,7 +7845,11 @@
           <t>16820424</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>16980000</t>
+        </is>
+      </c>
       <c r="G236" t="inlineStr"/>
     </row>
     <row r="237">
@@ -10131,12 +10131,12 @@
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>deh-estevao-lopes</t>
+          <t>deh-luis-de-sequeira</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Estêvão Lopes</t>
+          <t>Luís de Sequeira</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -10146,17 +10146,17 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Santo António da Terrugem, diocese de Elvas</t>
+          <t>Carcavelos</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>17080321</t>
+          <t>17090901</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>17140412</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="G309" t="inlineStr"/>
@@ -10164,12 +10164,12 @@
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>deh-estevao-lopes</t>
+          <t>deh-francisco-alberto</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Estêvão Lopes</t>
+          <t>Francisco Alberto</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -10179,17 +10179,17 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Santo António da Terrugem, diocese de Elvas</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>17080321</t>
+          <t>17100301</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17170417</t>
         </is>
       </c>
       <c r="G310" t="inlineStr"/>
@@ -10197,32 +10197,32 @@
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>deh-luis-de-sequeira</t>
+          <t>deh-antonio-maria-trigona</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Luís de Sequeira</t>
+          <t>Antonio-Maria Trigona</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Itália</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Carcavelos</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>17090901</t>
+          <t>17100621</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>17180416</t>
         </is>
       </c>
       <c r="G311" t="inlineStr"/>
@@ -10230,65 +10230,61 @@
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-alberto</t>
+          <t>deh-jean-sylvain-de-neuvialle</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Francisco Alberto</t>
+          <t>Jean Sylvain de Neuvialle</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>França</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>França</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>17100301</t>
-        </is>
-      </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>17170417</t>
-        </is>
-      </c>
+          <t>17110926</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr"/>
       <c r="G312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-maria-trigona</t>
+          <t>deh-agostinho-de-barros</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Antonio-Maria Trigona</t>
+          <t>Agostinho de Barros</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Arcos de Valdevez, diocese de Braga</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>17100621</t>
+          <t>17120212</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>17180416</t>
+          <t>17300404</t>
         </is>
       </c>
       <c r="G313" t="inlineStr"/>
@@ -10296,27 +10292,27 @@
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>deh-jean-sylvain-de-neuvialle</t>
+          <t>deh-jose-de-sousa</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Jean Sylvain de Neuvialle</t>
+          <t>José de Sousa</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>Múrcia, diocese de Braga</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>17110926</t>
+          <t>17120226</t>
         </is>
       </c>
       <c r="F314" t="inlineStr"/>
@@ -10325,45 +10321,41 @@
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>deh-agostinho-de-barros</t>
+          <t>deh-alexandre-de-la-charme</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Agostinho de Barros</t>
+          <t>Alexandre de La Charme</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>França</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Arcos de Valdevez, diocese de Braga</t>
+          <t>Lyon (rue de la Sirene)</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>17120212</t>
-        </is>
-      </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>17300404</t>
-        </is>
-      </c>
+          <t>17120907</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr"/>
       <c r="G315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>deh-jose-de-sousa</t>
+          <t>deh-policarpo-de-sousa</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>José de Sousa</t>
+          <t>Policarpo de Sousa</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -10373,26 +10365,30 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Múrcia, diocese de Braga</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>17120226</t>
-        </is>
-      </c>
-      <c r="F316" t="inlineStr"/>
+          <t>17121031</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>1725</t>
+        </is>
+      </c>
       <c r="G316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>deh-alexandre-de-la-charme</t>
+          <t>deh-jean-baptiste-batailhe</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Alexandre de La Charme</t>
+          <t>Jean-Baptiste Batailhé</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -10402,79 +10398,79 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Lyon (rue de la Sirene)</t>
+          <t>Albi</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>17120907</t>
-        </is>
-      </c>
-      <c r="F317" t="inlineStr"/>
+          <t>17130905</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>17301210</t>
+        </is>
+      </c>
       <c r="G317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>deh-policarpo-de-sousa</t>
+          <t>deh-valentin-chalier</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Policarpo de Sousa</t>
+          <t>Valentin Chalier</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>França</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Oulx, diocese de Turim</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>17121031</t>
-        </is>
-      </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>1725</t>
-        </is>
-      </c>
+          <t>17150909</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr"/>
       <c r="G318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>deh-jean-baptiste-batailhe</t>
+          <t>deh-pedro-de-figueiredo-ii</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Jean-Baptiste Batailhé</t>
+          <t>Pedro de Figueiredo</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Albi</t>
+          <t>Pombal</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>17130905</t>
+          <t>17160313</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>17301210</t>
+          <t>17160314</t>
         </is>
       </c>
       <c r="G319" t="inlineStr"/>
@@ -10482,12 +10478,12 @@
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>deh-valentin-chalier</t>
+          <t>deh-gabriel-boussel</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Valentin Chalier</t>
+          <t>Gabriel Boussel</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -10497,79 +10493,79 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Oulx, diocese de Turim</t>
+          <t>Diocese de Clermont, Auvergne</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>17150909</t>
-        </is>
-      </c>
-      <c r="F320" t="inlineStr"/>
+          <t>17171012</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>17321110</t>
+        </is>
+      </c>
       <c r="G320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>deh-pedro-de-figueiredo-ii</t>
+          <t>deh-joao-alvares</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Pedro de Figueiredo</t>
+          <t>João Álvares</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Pombal</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>17160313</t>
-        </is>
-      </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>17160314</t>
-        </is>
-      </c>
+          <t>17180000</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr"/>
       <c r="G321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>deh-gabriel-boussel</t>
+          <t>deh-francesco-folleri</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Gabriel Boussel</t>
+          <t>Francesco Folleri</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>Itália</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Diocese de Clermont, Auvergne</t>
+          <t>Florença</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>17171012</t>
+          <t>17180311</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>17321110</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="G322" t="inlineStr"/>
@@ -10577,61 +10573,65 @@
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-alvares</t>
+          <t>deh-martim-correa</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>João Álvares</t>
+          <t>Martim Correa</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>17180000</t>
-        </is>
-      </c>
-      <c r="F323" t="inlineStr"/>
+          <t>17200815</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>1725</t>
+        </is>
+      </c>
       <c r="G323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>deh-francesco-folleri</t>
+          <t>deh-anton-gogeisl</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Francesco Folleri</t>
+          <t>Anton Gogeisl</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>Alemanha</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Florença</t>
+          <t>Siegenburg, Baviera, diocese de Regensburg</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>17180311</t>
+          <t>17200913</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="G324" t="inlineStr"/>
@@ -10639,12 +10639,12 @@
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>deh-martim-correa</t>
+          <t>deh-fernando-pereira</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Martim Correa</t>
+          <t>Fernando Pereira</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -10654,17 +10654,17 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Rio Tinto, diocese do Porto</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>17200815</t>
+          <t>17210422</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>17490000</t>
         </is>
       </c>
       <c r="G325" t="inlineStr"/>
@@ -10672,65 +10672,61 @@
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>deh-anton-gogeisl</t>
+          <t>deh-louis-joseph-le-febure</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Anton Gogeisl</t>
+          <t>Louis-Joseph Le Febure</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>França</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Siegenburg, Baviera, diocese de Regensburg</t>
+          <t>Clisson</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>17200913</t>
-        </is>
-      </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>1737</t>
-        </is>
-      </c>
+          <t>17221118</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr"/>
       <c r="G326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>deh-fernando-pereira</t>
+          <t>deh-johann-siebert</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Fernando Pereira</t>
+          <t>Johann Siebert</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Boémia</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Rio Tinto, diocese do Porto</t>
+          <t>Jihlava</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>17210422</t>
+          <t>17231009</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>17490000</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="G327" t="inlineStr"/>
@@ -10738,61 +10734,65 @@
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>deh-louis-joseph-le-febure</t>
+          <t>deh-manuel-de-carvalho</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Louis-Joseph Le Febure</t>
+          <t>Manuel de Carvalho</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Clisson</t>
+          <t>Porto de Mós, diocese de Leiria</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>17221118</t>
-        </is>
-      </c>
-      <c r="F328" t="inlineStr"/>
+          <t>17240402</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>17320425</t>
+        </is>
+      </c>
       <c r="G328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>deh-johann-siebert</t>
+          <t>deh-joao-de-barros</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Johann Siebert</t>
+          <t>João de Barros</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Boémia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Jihlava</t>
+          <t>Gradil, diocese de Lisboa</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>17231009</t>
+          <t>17240402</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>17300404</t>
         </is>
       </c>
       <c r="G329" t="inlineStr"/>
@@ -10800,12 +10800,12 @@
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-de-barros</t>
+          <t>deh-inacio-francisco</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>João de Barros</t>
+          <t>Inácio Francisco</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -10815,17 +10815,17 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Gradil, diocese de Lisboa</t>
+          <t>Conraria, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>17240402</t>
+          <t>17240824</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>17300404</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="G330" t="inlineStr"/>
@@ -10833,45 +10833,41 @@
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-de-carvalho</t>
+          <t>deh-johann-hoppe</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Manuel de Carvalho</t>
+          <t>Johann Hoppe</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Alemanha</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Porto de Mós, diocese de Leiria</t>
+          <t>Schweidnitz, Silésia</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>17240402</t>
-        </is>
-      </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>17320425</t>
-        </is>
-      </c>
+          <t>17241020</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr"/>
       <c r="G331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t>deh-inacio-francisco</t>
+          <t>deh-luis-pereira</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Inácio Francisco</t>
+          <t>Luís Pereira</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -10881,59 +10877,59 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Conraria, diocese de Coimbra</t>
+          <t>?</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>17240824</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>1752</t>
-        </is>
-      </c>
+          <t>17251125</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr"/>
       <c r="G332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t>deh-johann-hoppe</t>
+          <t>deh-joao-de-lemos</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Johann Hoppe</t>
+          <t>João de Lemos</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Schweidnitz, Silésia</t>
+          <t>Quintela, diocese de Lamego</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>17241020</t>
-        </is>
-      </c>
-      <c r="F333" t="inlineStr"/>
+          <t>17260602</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>17300404</t>
+        </is>
+      </c>
       <c r="G333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t>deh-luis-pereira</t>
+          <t>deh-joao-de-lemos</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Luís Pereira</t>
+          <t>João de Lemos</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -10943,15 +10939,19 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Quintela, diocese de Lamego</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>17251125</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr"/>
+          <t>17260602</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>17320425</t>
+        </is>
+      </c>
       <c r="G334" t="inlineStr"/>
     </row>
     <row r="335">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>17300404</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="G335" t="inlineStr"/>
@@ -10990,12 +10990,12 @@
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-de-lemos</t>
+          <t>deh-joao-de-seixas</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>João de Lemos</t>
+          <t>João de Seixas</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -11005,17 +11005,17 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Quintela, diocese de Lamego</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>17260602</t>
+          <t>17271125</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>17320425</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="G336" t="inlineStr"/>
@@ -11023,12 +11023,12 @@
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-de-lemos</t>
+          <t>deh-felix-da-rocha</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>João de Lemos</t>
+          <t>Félix da Rocha</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -11038,17 +11038,17 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Quintela, diocese de Lamego</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>17260602</t>
+          <t>17280501</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>17350413</t>
         </is>
       </c>
       <c r="G337" t="inlineStr"/>
@@ -11056,32 +11056,32 @@
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-de-seixas</t>
+          <t>deh-sebastian-zwerger</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>João de Seixas</t>
+          <t>Sebastian Zwerger</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Alemanha</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Munique</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>17271125</t>
+          <t>17280913</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>17460000</t>
         </is>
       </c>
       <c r="G338" t="inlineStr"/>
@@ -11089,136 +11089,136 @@
     <row r="339">
       <c r="A339" s="1" t="inlineStr">
         <is>
-          <t>deh-felix-da-rocha</t>
+          <t>deh-herman-scolt</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Félix da Rocha</t>
+          <t>Herman Scolt</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>?</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>?</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>17280501</t>
-        </is>
-      </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>17350413</t>
-        </is>
-      </c>
+          <t>17281228</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr"/>
       <c r="G339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="1" t="inlineStr">
         <is>
-          <t>deh-sebastian-zwerger</t>
+          <t>deh-julien-xavier-tcheng</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Sebastian Zwerger</t>
+          <t>Julien Xavier Tch'eng</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Munique</t>
+          <t>Fukien</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>17280913</t>
-        </is>
-      </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>17460000</t>
-        </is>
-      </c>
+          <t>17290324</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr"/>
       <c r="G340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="1" t="inlineStr">
         <is>
-          <t>deh-herman-scolt</t>
+          <t>deh-manuel-viegas</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Herman Scolt</t>
+          <t>Manuel Viegas</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Marvão, diocese de Portalegre</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>17281228</t>
-        </is>
-      </c>
-      <c r="F341" t="inlineStr"/>
+          <t>17290731</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>1746</t>
+        </is>
+      </c>
       <c r="G341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="1" t="inlineStr">
         <is>
-          <t>deh-julien-xavier-tcheng</t>
+          <t>deh-manuel-jose</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Julien Xavier Tch'eng</t>
+          <t>Manuel José</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Fukien</t>
+          <t>Guemara, diocese de Braga</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>17290324</t>
-        </is>
-      </c>
-      <c r="F342" t="inlineStr"/>
+          <t>17290820</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>17350413</t>
+        </is>
+      </c>
       <c r="G342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-viegas</t>
+          <t>deh-jose-rosado</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Manuel Viegas</t>
+          <t>José Rosado</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -11228,17 +11228,17 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Marvão, diocese de Portalegre</t>
+          <t>Vimieiro, diocese de Évora</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>17290731</t>
+          <t>17291026</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>&gt;1755:&lt;1758</t>
         </is>
       </c>
       <c r="G343" t="inlineStr"/>
@@ -11246,93 +11246,85 @@
     <row r="344">
       <c r="A344" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-jose</t>
+          <t>deh-philippe-gonzaga</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Manuel José</t>
+          <t>Philippe Gonzaga</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Tonquim</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Guemara, diocese de Braga</t>
+          <t>Tonquim</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>17290820</t>
-        </is>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>17350413</t>
-        </is>
-      </c>
+          <t>17301027</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr"/>
       <c r="G344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="1" t="inlineStr">
         <is>
-          <t>deh-jose-rosado</t>
+          <t>deh-joseph-ferreira</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>José Rosado</t>
+          <t>Joseph Ferreira</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Vimieiro, diocese de Évora</t>
+          <t>?</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>17291026</t>
-        </is>
-      </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>&gt;1755:&lt;1758</t>
-        </is>
-      </c>
+          <t>1731</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr"/>
       <c r="G345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="1" t="inlineStr">
         <is>
-          <t>deh-philippe-gonzaga</t>
+          <t>deh-jean-francois-legalais</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Philippe Gonzaga</t>
+          <t>Jean-François Légalais</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Tonquim</t>
+          <t>França</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Tonquim</t>
+          <t>Bretanha</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>17301027</t>
+          <t>17310207</t>
         </is>
       </c>
       <c r="F346" t="inlineStr"/>
@@ -11341,12 +11333,12 @@
     <row r="347">
       <c r="A347" s="1" t="inlineStr">
         <is>
-          <t>deh-joseph-ferreira</t>
+          <t>deh-manuel-de-morais</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Joseph Ferreira</t>
+          <t>Manuel de Morais</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -11356,12 +11348,12 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>17310814</t>
         </is>
       </c>
       <c r="F347" t="inlineStr"/>
@@ -11370,90 +11362,98 @@
     <row r="348">
       <c r="A348" s="1" t="inlineStr">
         <is>
-          <t>deh-jean-francois-legalais</t>
+          <t>deh-onofrio-villiani</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Jean-François Légalais</t>
+          <t>Onofrio Villiani</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>Itália</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Bretanha</t>
+          <t>Faenza</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>17310207</t>
-        </is>
-      </c>
-      <c r="F348" t="inlineStr"/>
+          <t>17311016</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>1755</t>
+        </is>
+      </c>
       <c r="G348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-de-morais</t>
+          <t>deh-joao-de-loureiro</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Manuel de Morais</t>
+          <t>João de Loureiro</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>17310814</t>
-        </is>
-      </c>
-      <c r="F349" t="inlineStr"/>
+          <t>17320503</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>17350413</t>
+        </is>
+      </c>
       <c r="G349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="1" t="inlineStr">
         <is>
-          <t>deh-onofrio-villiani</t>
+          <t>deh-bento-monteiro</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Onofrio Villiani</t>
+          <t>Bento Monteiro</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Faenza</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>17311016</t>
+          <t>17320627</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>17350413</t>
         </is>
       </c>
       <c r="G350" t="inlineStr"/>
@@ -11461,65 +11461,61 @@
     <row r="351">
       <c r="A351" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-de-loureiro</t>
+          <t>deh-jean-francois-xavier-regis-tchen</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>João de Loureiro</t>
+          <t>Jean-François Xavier Régis Tch'en</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Cantão</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>17320503</t>
-        </is>
-      </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>17350413</t>
-        </is>
-      </c>
+          <t>17320907</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr"/>
       <c r="G351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="1" t="inlineStr">
         <is>
-          <t>deh-bento-monteiro</t>
+          <t>deh-franz-moser</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Bento Monteiro</t>
+          <t>Franz Moser</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Alemanha</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Mauerkirchen, dicese de Passau</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>17320627</t>
+          <t>17321003</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>17350413</t>
+          <t>17460000</t>
         </is>
       </c>
       <c r="G352" t="inlineStr"/>
@@ -11527,61 +11523,65 @@
     <row r="353">
       <c r="A353" s="1" t="inlineStr">
         <is>
-          <t>deh-jean-francois-xavier-regis-tchen</t>
+          <t>deh-franz-moser</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Jean-François Xavier Régis Tch'en</t>
+          <t>Franz Moser</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Alemanha</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Cantão</t>
+          <t>Mauerkirchen, dicese de Passau</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>17320907</t>
-        </is>
-      </c>
-      <c r="F353" t="inlineStr"/>
+          <t>17321003</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>17500000</t>
+        </is>
+      </c>
       <c r="G353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" s="1" t="inlineStr">
         <is>
-          <t>deh-franz-moser</t>
+          <t>deh-andre-nicolas-forgeot</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Franz Moser</t>
+          <t>André-Nicolas Forgeot</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>França</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Mauerkirchen, dicese de Passau</t>
+          <t>Borgonha</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>17321003</t>
+          <t>17330914</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>17460000</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="G354" t="inlineStr"/>
@@ -11589,65 +11589,61 @@
     <row r="355">
       <c r="A355" s="1" t="inlineStr">
         <is>
-          <t>deh-franz-moser</t>
+          <t>deh-gilles-thebault</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Franz Moser</t>
+          <t>Gilles Thébault</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>França</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Mauerkirchen, dicese de Passau</t>
+          <t>Saint-Malo</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>17321003</t>
-        </is>
-      </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>17500000</t>
-        </is>
-      </c>
+          <t>17331027</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr"/>
       <c r="G355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="1" t="inlineStr">
         <is>
-          <t>deh-andre-nicolas-forgeot</t>
+          <t>deh-manuel-gomes-formao</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>André-Nicolas Forgeot</t>
+          <t>Manuel Gomes Formão</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Borgonha</t>
+          <t>Melgaço, diocese de Braga</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>17330914</t>
+          <t>17340213</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="G356" t="inlineStr"/>
@@ -11655,41 +11651,45 @@
     <row r="357">
       <c r="A357" s="1" t="inlineStr">
         <is>
-          <t>deh-gilles-thebault</t>
+          <t>deh-manuel-gomes-formao</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Gilles Thébault</t>
+          <t>Manuel Gomes Formão</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Saint-Malo</t>
+          <t>Melgaço, diocese de Braga</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>17331027</t>
-        </is>
-      </c>
-      <c r="F357" t="inlineStr"/>
+          <t>17340213</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>1758</t>
+        </is>
+      </c>
       <c r="G357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-gomes-formao</t>
+          <t>deh-joao-simoes</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Manuel Gomes Formão</t>
+          <t>João Simões</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -11699,17 +11699,17 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Melgaço, diocese de Braga</t>
+          <t>Penela, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>17340213</t>
+          <t>17340517</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="G358" t="inlineStr"/>
@@ -11717,45 +11717,41 @@
     <row r="359">
       <c r="A359" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-gomes-formao</t>
+          <t>deh-pierre-tchen</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Manuel Gomes Formão</t>
+          <t>Pierre T'chen</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Melgaço, diocese de Braga</t>
+          <t>Soochow, Kiang-nan</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>17340213</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>1758</t>
-        </is>
-      </c>
+          <t>17340803</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr"/>
       <c r="G359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-simoes</t>
+          <t>deh-domingos-da-silva</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>João Simões</t>
+          <t>Domingos da Silva</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -11765,74 +11761,74 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Penela, diocese de Coimbra</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>17340517</t>
-        </is>
-      </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>1741</t>
-        </is>
-      </c>
+          <t>17341031</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr"/>
       <c r="G360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="1" t="inlineStr">
         <is>
-          <t>deh-pierre-tchen</t>
+          <t>deh-luis-de-moura</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Pierre T'chen</t>
+          <t>Luís de Moura</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Soochow, Kiang-nan</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>17340803</t>
-        </is>
-      </c>
-      <c r="F361" t="inlineStr"/>
+          <t>17350000</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>16440412</t>
+        </is>
+      </c>
       <c r="G361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="1" t="inlineStr">
         <is>
-          <t>deh-domingos-da-silva</t>
+          <t>deh-joseph-tcheou</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Domingos da Silva</t>
+          <t>Joseph Tcheou</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Nanquim</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>17341031</t>
+          <t>17350207</t>
         </is>
       </c>
       <c r="F362" t="inlineStr"/>
@@ -11841,12 +11837,12 @@
     <row r="363">
       <c r="A363" s="1" t="inlineStr">
         <is>
-          <t>deh-luis-de-moura</t>
+          <t>deh-bartolomeu-de-azevedo</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Luís de Moura</t>
+          <t>Bartolomeu de Azevedo</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -11856,17 +11852,17 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Viana do Castelo</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>17350000</t>
+          <t>17360322</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>16440412</t>
+          <t>17440000</t>
         </is>
       </c>
       <c r="G363" t="inlineStr"/>
@@ -11874,61 +11870,65 @@
     <row r="364">
       <c r="A364" s="1" t="inlineStr">
         <is>
-          <t>deh-joseph-tcheou</t>
+          <t>deh-manuel-da-motta</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Joseph Tcheou</t>
+          <t>Manuel da Motta</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Nanquim</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>17350207</t>
-        </is>
-      </c>
-      <c r="F364" t="inlineStr"/>
+          <t>17360519</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>17480000</t>
+        </is>
+      </c>
       <c r="G364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="1" t="inlineStr">
         <is>
-          <t>deh-bartolomeu-de-azevedo</t>
+          <t>deh-ignaz-sichelbarth</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Bartolomeu de Azevedo</t>
+          <t>Ignaz Sichelbarth</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Boémia</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Viana do Castelo</t>
+          <t>Neudeck, Boémia</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>17360322</t>
+          <t>17361020</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>17440000</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="G365" t="inlineStr"/>
@@ -11936,12 +11936,12 @@
     <row r="366">
       <c r="A366" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-da-motta</t>
+          <t>deh-xavier-duarte</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Manuel da Motta</t>
+          <t>Xavier Duarte</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -11951,17 +11951,17 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>17360519</t>
+          <t>17361103</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>17480000</t>
+          <t>17420000</t>
         </is>
       </c>
       <c r="G366" t="inlineStr"/>
@@ -11969,32 +11969,32 @@
     <row r="367">
       <c r="A367" s="1" t="inlineStr">
         <is>
-          <t>deh-ignaz-sichelbarth</t>
+          <t>deh-paulo-de-campos</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Ignaz Sichelbarth</t>
+          <t>Paulo de Campos</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Boémia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Neudeck, Boémia</t>
+          <t>Bobadela, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>17361020</t>
+          <t>17370502</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="G367" t="inlineStr"/>
@@ -12002,107 +12002,103 @@
     <row r="368">
       <c r="A368" s="1" t="inlineStr">
         <is>
-          <t>deh-xavier-duarte</t>
+          <t>deh-francois-vincent-yang</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Xavier Duarte</t>
+          <t>François Vincent Yang</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Nanquim</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>17361103</t>
-        </is>
-      </c>
-      <c r="F368" t="inlineStr">
-        <is>
-          <t>17420000</t>
-        </is>
-      </c>
+          <t>17370715</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr"/>
       <c r="G368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="1" t="inlineStr">
         <is>
-          <t>deh-paulo-de-campos</t>
+          <t>deh-antonio-de-barros-ii</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Paulo de Campos</t>
+          <t>António de Barros</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Bobadela, diocese de Coimbra</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>17370502</t>
-        </is>
-      </c>
-      <c r="F369" t="inlineStr">
-        <is>
-          <t>1746</t>
-        </is>
-      </c>
+          <t>17370907</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr"/>
       <c r="G369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="1" t="inlineStr">
         <is>
-          <t>deh-francois-vincent-yang</t>
+          <t>deh-dionisio-ferreira</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>François Vincent Yang</t>
+          <t>Dionísio Ferreira</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Nanquim</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>17370715</t>
-        </is>
-      </c>
-      <c r="F370" t="inlineStr"/>
+          <t>17380205</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>1745</t>
+        </is>
+      </c>
       <c r="G370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-de-barros-ii</t>
+          <t>deh-stanislas-monteiro</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>António de Barros</t>
+          <t>Stanislas Monteiro</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -12112,12 +12108,12 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>T'ai-yuan fou, Shansi</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>17370907</t>
+          <t>17380713</t>
         </is>
       </c>
       <c r="F371" t="inlineStr"/>
@@ -12126,60 +12122,56 @@
     <row r="372">
       <c r="A372" s="1" t="inlineStr">
         <is>
-          <t>deh-dionisio-ferreira</t>
+          <t>deh-jean-silva-peng</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Dionísio Ferreira</t>
+          <t>Jean Silva P'eng</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Pequim</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>17380205</t>
-        </is>
-      </c>
-      <c r="F372" t="inlineStr">
-        <is>
-          <t>1745</t>
-        </is>
-      </c>
+          <t>17380713</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr"/>
       <c r="G372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="1" t="inlineStr">
         <is>
-          <t>deh-stanislas-monteiro</t>
+          <t>deh-gabriel-leonard-de-brossard</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Stanislas Monteiro</t>
+          <t>Gabriel-Léonard de Brossard</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>França</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>T'ai-yuan fou, Shansi</t>
+          <t>Perche, diocese de Chartres</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>17380713</t>
+          <t>17381005</t>
         </is>
       </c>
       <c r="F373" t="inlineStr"/>
@@ -12188,27 +12180,27 @@
     <row r="374">
       <c r="A374" s="1" t="inlineStr">
         <is>
-          <t>deh-jean-silva-peng</t>
+          <t>deh-manuel-goncalves</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Jean Silva P'eng</t>
+          <t>Manuel Gonçalves</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Pequim</t>
+          <t>?</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>17380713</t>
+          <t>17390810</t>
         </is>
       </c>
       <c r="F374" t="inlineStr"/>
@@ -12217,41 +12209,45 @@
     <row r="375">
       <c r="A375" s="1" t="inlineStr">
         <is>
-          <t>deh-gabriel-leonard-de-brossard</t>
+          <t>deh-gregorio-seco</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Gabriel-Léonard de Brossard</t>
+          <t>Gregório Seco</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Perche, diocese de Chartres</t>
+          <t>Miranda do Corvo, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>17381005</t>
-        </is>
-      </c>
-      <c r="F375" t="inlineStr"/>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>1749</t>
+        </is>
+      </c>
       <c r="G375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-goncalves</t>
+          <t>deh-agostinho-da-silva</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Manuel Gonçalves</t>
+          <t>Agostinho da Silva</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -12261,26 +12257,30 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>17390810</t>
-        </is>
-      </c>
-      <c r="F376" t="inlineStr"/>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>1749</t>
+        </is>
+      </c>
       <c r="G376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="1" t="inlineStr">
         <is>
-          <t>deh-gregorio-seco</t>
+          <t>deh-jose-da-silva</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Gregório Seco</t>
+          <t>José da Silva</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Miranda do Corvo, diocese de Coimbra</t>
+          <t>Soure, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>17400225</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -12303,87 +12303,79 @@
           <t>1749</t>
         </is>
       </c>
-      <c r="G377" t="inlineStr"/>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>MMHM:p.375</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="inlineStr">
         <is>
-          <t>deh-agostinho-da-silva</t>
+          <t>deh-thomas-soares</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Agostinho da Silva</t>
+          <t>Thomas Soares</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Pequim</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>1740</t>
-        </is>
-      </c>
-      <c r="F378" t="inlineStr">
-        <is>
-          <t>1749</t>
-        </is>
-      </c>
+          <t>17401031</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr"/>
       <c r="G378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="1" t="inlineStr">
         <is>
-          <t>deh-jose-da-silva</t>
+          <t>deh-thaddee-xavier</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>José da Silva</t>
+          <t>Thaddée Xavier</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Soure, diocese de Coimbra</t>
+          <t>Pequim</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>17400225</t>
-        </is>
-      </c>
-      <c r="F379" t="inlineStr">
-        <is>
-          <t>1749</t>
-        </is>
-      </c>
-      <c r="G379" t="inlineStr">
-        <is>
-          <t>MMHM:p.375</t>
-        </is>
-      </c>
+          <t>17401101</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr"/>
+      <c r="G379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="1" t="inlineStr">
         <is>
-          <t>deh-thomas-soares</t>
+          <t>deh-francois-da-cunha-hiu</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Thomas Soares</t>
+          <t>François da Cunha Hiu</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -12393,12 +12385,12 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Pequim</t>
+          <t>Kiangnan</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>17401031</t>
+          <t>17401102</t>
         </is>
       </c>
       <c r="F380" t="inlineStr"/>
@@ -12407,41 +12399,45 @@
     <row r="381">
       <c r="A381" s="1" t="inlineStr">
         <is>
-          <t>deh-thaddee-xavier</t>
+          <t>deh-jose-de-araujo</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Thaddée Xavier</t>
+          <t>José de Araújo</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Pequim</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>17401101</t>
-        </is>
-      </c>
-      <c r="F381" t="inlineStr"/>
+          <t>17410327</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>17490000</t>
+        </is>
+      </c>
       <c r="G381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="1" t="inlineStr">
         <is>
-          <t>deh-francois-da-cunha-hiu</t>
+          <t>deh-joseph-de-aguiar-souen</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>François da Cunha Hiu</t>
+          <t>Joseph de Aguiar Souen</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -12451,12 +12447,12 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Kiangnan</t>
+          <t>Changshu, Kiang-sou, China</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>17401102</t>
+          <t>17420921</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
@@ -12465,136 +12461,136 @@
     <row r="383">
       <c r="A383" s="1" t="inlineStr">
         <is>
-          <t>deh-jose-de-araujo</t>
+          <t>deh-marc-ribeiro-kouan</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>José de Araújo</t>
+          <t>Marc Ribeiro Kouan</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Soochow (Sou-tcheou fou), Kiangnan</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>17410327</t>
-        </is>
-      </c>
-      <c r="F383" t="inlineStr">
-        <is>
-          <t>17490000</t>
-        </is>
-      </c>
+          <t>17420921</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr"/>
       <c r="G383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="1" t="inlineStr">
         <is>
-          <t>deh-joseph-de-aguiar-souen</t>
+          <t>deh-antonio-saverio-falcao</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Joseph de Aguiar Souen</t>
+          <t>António Saverio Falcão</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Changshu, Kiang-sou, China</t>
+          <t>Diocese da Guarda</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>17420921</t>
-        </is>
-      </c>
-      <c r="F384" t="inlineStr"/>
+          <t>17430710</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>1752</t>
+        </is>
+      </c>
       <c r="G384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="1" t="inlineStr">
         <is>
-          <t>deh-marc-ribeiro-kouan</t>
+          <t>deh-jose-galvao</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Marc Ribeiro Kouan</t>
+          <t>José Galvão</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Soochow (Sou-tcheou fou), Kiangnan</t>
+          <t>?</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>17420921</t>
-        </is>
-      </c>
-      <c r="F385" t="inlineStr"/>
+          <t>17431016</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>1749</t>
+        </is>
+      </c>
       <c r="G385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-saverio-falcao</t>
+          <t>deh-jean-baptiste-gentil-de-brassaud</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>António Saverio Falcão</t>
+          <t>Jean-Baptiste Gentil de Brassaud</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>França</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Diocese da Guarda</t>
+          <t>Xanto, Saintonge</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>17430710</t>
-        </is>
-      </c>
-      <c r="F386" t="inlineStr">
-        <is>
-          <t>1752</t>
-        </is>
-      </c>
+          <t>17431220</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr"/>
       <c r="G386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="1" t="inlineStr">
         <is>
-          <t>deh-jose-galvao</t>
+          <t>deh-mateus-de-figueiredo</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>José Galvão</t>
+          <t>Mateus de Figueiredo</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -12604,59 +12600,59 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>S. Joaninho, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>17431016</t>
-        </is>
-      </c>
-      <c r="F387" t="inlineStr">
-        <is>
-          <t>1749</t>
-        </is>
-      </c>
+          <t>17440404</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr"/>
       <c r="G387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="1" t="inlineStr">
         <is>
-          <t>deh-jean-baptiste-gentil-de-brassaud</t>
+          <t>deh-luis-de-carvalho-i</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Jean-Baptiste Gentil de Brassaud</t>
+          <t>Luís de Carvalho</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Xanto, Saintonge</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>17431220</t>
+          <t>17440827</t>
         </is>
       </c>
       <c r="F388" t="inlineStr"/>
-      <c r="G388" t="inlineStr"/>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>marcado destinado à China em 1749</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="inlineStr">
         <is>
-          <t>deh-mateus-de-figueiredo</t>
+          <t>deh-francisco-pina</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Mateus de Figueiredo</t>
+          <t>Francisco Pina</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -12666,12 +12662,12 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>S. Joaninho, diocese de Coimbra</t>
+          <t>Évora</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>17440404</t>
+          <t>17450930</t>
         </is>
       </c>
       <c r="F389" t="inlineStr"/>
@@ -12680,45 +12676,41 @@
     <row r="390">
       <c r="A390" s="1" t="inlineStr">
         <is>
-          <t>deh-luis-de-carvalho-i</t>
+          <t>deh-victor-agricola-poisson</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Luís de Carvalho</t>
+          <t>Victor-Agricola Poisson</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>França</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Billom, diocese de Clermont</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>17440827</t>
+          <t>17451014</t>
         </is>
       </c>
       <c r="F390" t="inlineStr"/>
-      <c r="G390" t="inlineStr">
-        <is>
-          <t>marcado destinado à China em 1749</t>
-        </is>
-      </c>
+      <c r="G390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-pina</t>
+          <t>deh-francisco-da-silva-iii</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Francisco Pina</t>
+          <t>Francisco da Silva</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -12728,41 +12720,45 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Évora</t>
+          <t>Vinha da Rainha, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>17450930</t>
-        </is>
-      </c>
-      <c r="F391" t="inlineStr"/>
+          <t>17451103</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>1754</t>
+        </is>
+      </c>
       <c r="G391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="1" t="inlineStr">
         <is>
-          <t>deh-victor-agricola-poisson</t>
+          <t>deh-agostinho-de-avellar</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Victor-Agricola Poisson</t>
+          <t>Agostinho de Avellar</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Billom, diocese de Clermont</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>17451014</t>
+          <t>17451207</t>
         </is>
       </c>
       <c r="F392" t="inlineStr"/>
@@ -12771,12 +12767,12 @@
     <row r="393">
       <c r="A393" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-da-silva-iii</t>
+          <t>deh-antonio-simoes-ii</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Francisco da Silva</t>
+          <t>António Simões</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -12786,30 +12782,26 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Vinha da Rainha, diocese de Coimbra</t>
+          <t>Vouzela, diocese de Viseu</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>17451103</t>
-        </is>
-      </c>
-      <c r="F393" t="inlineStr">
-        <is>
-          <t>1754</t>
-        </is>
-      </c>
+          <t>17460115</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr"/>
       <c r="G393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="1" t="inlineStr">
         <is>
-          <t>deh-agostinho-de-avellar</t>
+          <t>deh-simao-de-almeida</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Agostinho de Avellar</t>
+          <t>Simão de Almeida</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -12819,12 +12811,12 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Viseu</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>17451207</t>
+          <t>17460318</t>
         </is>
       </c>
       <c r="F394" t="inlineStr"/>
@@ -12833,12 +12825,12 @@
     <row r="395">
       <c r="A395" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-simoes-ii</t>
+          <t>deh-luis-duarte</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>António Simões</t>
+          <t>Luís Duarte</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -12848,26 +12840,30 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Vouzela, diocese de Viseu</t>
+          <t>Rio de Vide, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>17460115</t>
-        </is>
-      </c>
-      <c r="F395" t="inlineStr"/>
+          <t>17460519</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>17530000</t>
+        </is>
+      </c>
       <c r="G395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="1" t="inlineStr">
         <is>
-          <t>deh-simao-de-almeida</t>
+          <t>deh-joaquim-de-azevedo</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Simão de Almeida</t>
+          <t>Joaquim de Azevedo</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -12877,12 +12873,12 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Viseu</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>17460318</t>
+          <t>17460615</t>
         </is>
       </c>
       <c r="F396" t="inlineStr"/>
@@ -12891,12 +12887,12 @@
     <row r="397">
       <c r="A397" s="1" t="inlineStr">
         <is>
-          <t>deh-luis-duarte</t>
+          <t>deh-antonio-simoes-iii</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Luís Duarte</t>
+          <t>António Simões</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -12906,17 +12902,17 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Rio de Vide, diocese de Coimbra</t>
+          <t>Penela, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>17460519</t>
+          <t>17460615</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>17530000</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="G397" t="inlineStr"/>
@@ -12924,12 +12920,12 @@
     <row r="398">
       <c r="A398" s="1" t="inlineStr">
         <is>
-          <t>deh-joaquim-de-azevedo</t>
+          <t>deh-antonio-simoes-iii</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Joaquim de Azevedo</t>
+          <t>António Simões</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -12939,7 +12935,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Penela, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -12947,18 +12943,22 @@
           <t>17460615</t>
         </is>
       </c>
-      <c r="F398" t="inlineStr"/>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>1758</t>
+        </is>
+      </c>
       <c r="G398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-simoes-iii</t>
+          <t>deh-tome-da-silva</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>António Simões</t>
+          <t>Tomé da Silva</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -12968,17 +12968,17 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Penela, diocese de Coimbra</t>
+          <t>Sousa, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>17460615</t>
+          <t>17460719</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="G399" t="inlineStr"/>
@@ -12986,12 +12986,12 @@
     <row r="400">
       <c r="A400" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-simoes-iii</t>
+          <t>deh-manuel-de-carvalho-ii</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>António Simões</t>
+          <t>Manuel de Carvalho</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -13001,30 +13001,30 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Penela, diocese de Coimbra</t>
+          <t>Águeda, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>17460615</t>
-        </is>
-      </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>1758</t>
-        </is>
-      </c>
-      <c r="G400" t="inlineStr"/>
+          <t>17470102</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>talvez tenha saído durante o noviciado</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="inlineStr">
         <is>
-          <t>deh-tome-da-silva</t>
+          <t>deh-manuel-de-silva</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Tomé da Silva</t>
+          <t>Manuel de Silva</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -13034,17 +13034,17 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Sousa, diocese de Coimbra</t>
+          <t>Tomar</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>17460719</t>
+          <t>17470406</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>1753</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="G401" t="inlineStr"/>
@@ -13052,45 +13052,41 @@
     <row r="402">
       <c r="A402" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-de-carvalho-ii</t>
+          <t>deh-francois-xavier-cuinh</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Manuel de Carvalho</t>
+          <t>François Xavier Cuinh</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Tonquim</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Águeda, diocese de Coimbra</t>
+          <t>Tonquim</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>17470102</t>
+          <t>17470814</t>
         </is>
       </c>
       <c r="F402" t="inlineStr"/>
-      <c r="G402" t="inlineStr">
-        <is>
-          <t>talvez tenha saído durante o noviciado</t>
-        </is>
-      </c>
+      <c r="G402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-de-silva</t>
+          <t>deh-joao-da-fonseca-ii</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Manuel de Silva</t>
+          <t>João da Fonseca</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -13100,17 +13096,17 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Tomar</t>
+          <t>Villacova de Suevo, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>17470406</t>
+          <t>17480518</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="G403" t="inlineStr"/>
@@ -13118,27 +13114,27 @@
     <row r="404">
       <c r="A404" s="1" t="inlineStr">
         <is>
-          <t>deh-francois-xavier-cuinh</t>
+          <t>deh-pierre-vaquier-la-baume</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>François Xavier Cuinh</t>
+          <t>Pierre Vaquier La Baume</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Tonquim</t>
+          <t>França</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Tonquim</t>
+          <t>Diocese de Rodez</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>17470814</t>
+          <t>17481005</t>
         </is>
       </c>
       <c r="F404" t="inlineStr"/>
@@ -13147,12 +13143,12 @@
     <row r="405">
       <c r="A405" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-da-fonseca-ii</t>
+          <t>deh-manuel-da-costa</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>João da Fonseca</t>
+          <t>Manuel da Costa</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -13162,74 +13158,74 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Villacova de Suevo, diocese de Coimbra</t>
+          <t>Figueiró, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>17480518</t>
-        </is>
-      </c>
-      <c r="F405" t="inlineStr">
-        <is>
-          <t>1753</t>
-        </is>
-      </c>
+          <t>17481209</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr"/>
       <c r="G405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="1" t="inlineStr">
         <is>
-          <t>deh-pierre-vaquier-la-baume</t>
+          <t>deh-francisco-pinto-ii</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Pierre Vaquier La Baume</t>
+          <t>Francisco Pinto</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Diocese de Rodez</t>
+          <t>Galafura, diocese de Braga</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>17481005</t>
-        </is>
-      </c>
-      <c r="F406" t="inlineStr"/>
+          <t>17490131</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>&gt;1755:&lt;1758</t>
+        </is>
+      </c>
       <c r="G406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-da-costa</t>
+          <t>deh-symphorien-duarte</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Manuel da Costa</t>
+          <t>Symphorien Duarte</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Figueiró, diocese de Coimbra</t>
+          <t>Hangchow, Chekiang</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>17481209</t>
+          <t>17490201</t>
         </is>
       </c>
       <c r="F407" t="inlineStr"/>
@@ -13238,60 +13234,56 @@
     <row r="408">
       <c r="A408" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-pinto-ii</t>
+          <t>deh-jose-correa-tcheou</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Francisco Pinto</t>
+          <t>José Correa Tcheou</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Galafura, diocese de Braga</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>17490131</t>
-        </is>
-      </c>
-      <c r="F408" t="inlineStr">
-        <is>
-          <t>&gt;1755:&lt;1758</t>
-        </is>
-      </c>
+          <t>17490201</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr"/>
       <c r="G408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" s="1" t="inlineStr">
         <is>
-          <t>deh-jose-correa-tcheou</t>
+          <t>deh-luis-de-carvalho-ii</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>José Correa Tcheou</t>
+          <t>Luís de Carvalho</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>Miranda do Corvo, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>17490201</t>
+          <t>17490327</t>
         </is>
       </c>
       <c r="F409" t="inlineStr"/>
@@ -13300,12 +13292,12 @@
     <row r="410">
       <c r="A410" s="1" t="inlineStr">
         <is>
-          <t>deh-symphorien-duarte</t>
+          <t>deh-jose-felix</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Symphorien Duarte</t>
+          <t>José Félix</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -13315,12 +13307,12 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Hangchow, Chekiang</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>17490201</t>
+          <t>17491207</t>
         </is>
       </c>
       <c r="F410" t="inlineStr"/>
@@ -13329,27 +13321,27 @@
     <row r="411">
       <c r="A411" s="1" t="inlineStr">
         <is>
-          <t>deh-luis-de-carvalho-ii</t>
+          <t>deh-joao-de-sousa</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Luís de Carvalho</t>
+          <t>João de Sousa</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Miranda do Corvo, diocese de Coimbra</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>17490327</t>
+          <t>17491207</t>
         </is>
       </c>
       <c r="F411" t="inlineStr"/>
@@ -13358,12 +13350,12 @@
     <row r="412">
       <c r="A412" s="1" t="inlineStr">
         <is>
-          <t>deh-jose-felix</t>
+          <t>deh-manuel-lopes</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>José Félix</t>
+          <t>Manuel Lopes</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -13387,27 +13379,27 @@
     <row r="413">
       <c r="A413" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-lopes</t>
+          <t>deh-jose-de-almeida-iii</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Manuel Lopes</t>
+          <t>José de Almeida</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>Arcos, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>17491207</t>
+          <t>1750000</t>
         </is>
       </c>
       <c r="F413" t="inlineStr"/>
@@ -13416,27 +13408,27 @@
     <row r="414">
       <c r="A414" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-de-sousa</t>
+          <t>deh-jean-claude-beguin</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>João de Sousa</t>
+          <t>Jean Claude Béguin</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>França</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>Marcy-sous-Marle, diocese de Laon</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>17491207</t>
+          <t>17530121</t>
         </is>
       </c>
       <c r="F414" t="inlineStr"/>
@@ -13445,27 +13437,27 @@
     <row r="415">
       <c r="A415" s="1" t="inlineStr">
         <is>
-          <t>deh-jose-de-almeida-iii</t>
+          <t>deh-hubert-cousin-de-mericourt</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>José de Almeida</t>
+          <t>Hubert Cousin de Méricourt</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>França</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Arcos, diocese de Coimbra</t>
+          <t>Montdidier</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>1750000</t>
+          <t>17540108</t>
         </is>
       </c>
       <c r="F415" t="inlineStr"/>
@@ -13474,12 +13466,12 @@
     <row r="416">
       <c r="A416" s="1" t="inlineStr">
         <is>
-          <t>deh-jean-claude-beguin</t>
+          <t>deh-jean-matthieu-tournu-ventavon</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Jean Claude Béguin</t>
+          <t>Jean-Matthieu Tournu Ventavon</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -13489,12 +13481,12 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Marcy-sous-Marle, diocese de Laon</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>17530121</t>
+          <t>17541122</t>
         </is>
       </c>
       <c r="F416" t="inlineStr"/>
@@ -13503,12 +13495,12 @@
     <row r="417">
       <c r="A417" s="1" t="inlineStr">
         <is>
-          <t>deh-hubert-cousin-de-mericourt</t>
+          <t>deh-leon-pascal-baron</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Hubert Cousin de Méricourt</t>
+          <t>Léon-Pascal Baron</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -13518,198 +13510,140 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Montdidier</t>
+          <t>Carcassone</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>17540108</t>
-        </is>
-      </c>
-      <c r="F417" t="inlineStr"/>
+          <t>17570406</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>17660118</t>
+        </is>
+      </c>
       <c r="G417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="1" t="inlineStr">
         <is>
-          <t>deh-jean-matthieu-tournu-ventavon</t>
+          <t>deh-luigi-cipolla</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Jean-Matthieu Tournu Ventavon</t>
+          <t>Luigi Cipolla</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>Itália</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Caltavuturo, Palermo</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>17541122</t>
-        </is>
-      </c>
-      <c r="F418" t="inlineStr"/>
+          <t>17571105</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>17700320</t>
+        </is>
+      </c>
       <c r="G418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" s="1" t="inlineStr">
         <is>
-          <t>deh-leon-pascal-baron</t>
+          <t>deh-paolo-agostino-amoretti</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Léon-Pascal Baron</t>
+          <t>Paolo-Agostino Amoretti</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>Itália</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Carcassone</t>
+          <t>San Remo</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>17570406</t>
-        </is>
-      </c>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>17660118</t>
-        </is>
-      </c>
+          <t>17581126</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr"/>
       <c r="G419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="1" t="inlineStr">
         <is>
-          <t>deh-luigi-cipolla</t>
+          <t>deh-hyacinthe-paul-lieou-junior</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Luigi Cipolla</t>
+          <t>Hyacinthe Paul Lieou, júnior</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Caltavuturo, Palermo</t>
+          <t>Hukwang</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>17571105</t>
-        </is>
-      </c>
-      <c r="F420" t="inlineStr">
-        <is>
-          <t>17700320</t>
-        </is>
-      </c>
+          <t>17630930</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr"/>
       <c r="G420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="1" t="inlineStr">
         <is>
-          <t>deh-paolo-agostino-amoretti</t>
+          <t>deh-norbert-korsak</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Paolo-Agostino Amoretti</t>
+          <t>Norbert Korsak</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>Polónia</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>San Remo</t>
+          <t>Polotsk, Bielorrússia</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>17581126</t>
+          <t>17880828</t>
         </is>
       </c>
       <c r="F421" t="inlineStr"/>
       <c r="G421" t="inlineStr"/>
-    </row>
-    <row r="422">
-      <c r="A422" s="1" t="inlineStr">
-        <is>
-          <t>deh-hyacinthe-paul-lieou-junior</t>
-        </is>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>Hyacinthe Paul Lieou, júnior</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>Hukwang</t>
-        </is>
-      </c>
-      <c r="E422" t="inlineStr">
-        <is>
-          <t>17630930</t>
-        </is>
-      </c>
-      <c r="F422" t="inlineStr"/>
-      <c r="G422" t="inlineStr"/>
-    </row>
-    <row r="423">
-      <c r="A423" s="1" t="inlineStr">
-        <is>
-          <t>deh-norbert-korsak</t>
-        </is>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>Norbert Korsak</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>Polónia</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>Polotsk, Bielorrússia</t>
-        </is>
-      </c>
-      <c r="E423" t="inlineStr">
-        <is>
-          <t>17880828</t>
-        </is>
-      </c>
-      <c r="F423" t="inlineStr"/>
-      <c r="G423" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
